--- a/Data.xlsx
+++ b/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trò chơi\KNKX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DEE515E-16F7-4B47-AAB0-26D1F1F62004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747D2AA9-F0AC-4C74-A196-9B65CD2FFC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{CED7E1C3-DCFC-416D-B7FF-47B2F4A0DC54}"/>
   </bookViews>
